--- a/03_Group_comparisons/Muscle_strength/03_Set_Contrasts/c_data/set_contrasts.xlsx
+++ b/03_Group_comparisons/Muscle_strength/03_Set_Contrasts/c_data/set_contrasts.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11458" uniqueCount="3076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11491" uniqueCount="3096">
   <si>
     <t>sheet</t>
   </si>
@@ -8792,7 +8792,7 @@
     <t>fit</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Muscle_strength/03_Protein_Contrasts/c_data/fit.rds</t>
+    <t>03_Group_comparisons/Muscle_strength/02_Protein_Contrasts/c_data/fit.rds</t>
   </si>
   <si>
     <t>293a41d7ef36de7179b42dc1f593e3d3</t>
@@ -8801,7 +8801,7 @@
     <t>design</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Muscle_strength/02_Design_Contrasts/c_data/design.rds</t>
+    <t>03_Group_comparisons/Muscle_strength/01_Design_Contrasts/c_data/design.rds</t>
   </si>
   <si>
     <t>c0cfb05785ba25feadb966caf1fa5a50</t>
@@ -8825,7 +8825,7 @@
     <t>phenotype</t>
   </si>
   <si>
-    <t>00_Input/phenotype.csv</t>
+    <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
     <t>5a1989db406daa0b70189a9f0df52cf3</t>
@@ -8954,12 +8954,21 @@
     <t>Github (Dustyn-T-Lewis/enrichVolcano@d3fed631f4ae95e01bd61137699313f8de5cc86e)</t>
   </si>
   <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <t>1.0.5</t>
+  </si>
+  <si>
     <t>farver</t>
   </si>
   <si>
     <t>2.1.2</t>
   </si>
   <si>
+    <t>fastmap</t>
+  </si>
+  <si>
     <t>fastmatch</t>
   </si>
   <si>
@@ -9020,6 +9029,18 @@
     <t>1.1.4</t>
   </si>
   <si>
+    <t>htmltools</t>
+  </si>
+  <si>
+    <t>0.5.9</t>
+  </si>
+  <si>
+    <t>htmlwidgets</t>
+  </si>
+  <si>
+    <t>1.6.4</t>
+  </si>
+  <si>
     <t>IRanges</t>
   </si>
   <si>
@@ -9032,6 +9053,18 @@
     <t>1.0.14</t>
   </si>
   <si>
+    <t>jsonlite</t>
+  </si>
+  <si>
+    <t>2.0.0</t>
+  </si>
+  <si>
+    <t>knitr</t>
+  </si>
+  <si>
+    <t>1.51</t>
+  </si>
+  <si>
     <t>labeling</t>
   </si>
   <si>
@@ -9047,9 +9080,6 @@
     <t>lifecycle</t>
   </si>
   <si>
-    <t>1.0.5</t>
-  </si>
-  <si>
     <t>limma</t>
   </si>
   <si>
@@ -9074,6 +9104,12 @@
     <t>1.5.0</t>
   </si>
   <si>
+    <t>otel</t>
+  </si>
+  <si>
+    <t>0.2.0</t>
+  </si>
+  <si>
     <t>pillar</t>
   </si>
   <si>
@@ -9158,6 +9194,12 @@
     <t>CRAN (R 4.6.1)</t>
   </si>
   <si>
+    <t>rmarkdown</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
     <t>rprojroot</t>
   </si>
   <si>
@@ -9233,6 +9275,12 @@
     <t>0.5.0</t>
   </si>
   <si>
+    <t>utf8</t>
+  </si>
+  <si>
+    <t>1.2.6</t>
+  </si>
+  <si>
     <t>vctrs</t>
   </si>
   <si>
@@ -9249,6 +9297,18 @@
   </si>
   <si>
     <t>3.0.2</t>
+  </si>
+  <si>
+    <t>xfun</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>yaml</t>
+  </si>
+  <si>
+    <t>2.3.12</t>
   </si>
 </sst>
 </file>
@@ -75574,7 +75634,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -75821,13 +75881,13 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>91</v>
+        <v>2981</v>
       </c>
       <c r="B23" t="s">
-        <v>2981</v>
+        <v>2963</v>
       </c>
       <c r="C23" t="s">
-        <v>2938</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -75843,21 +75903,21 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" t="s">
         <v>2984</v>
       </c>
-      <c r="B25" t="s">
-        <v>2985</v>
-      </c>
       <c r="C25" t="s">
-        <v>2941</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>2985</v>
+      </c>
+      <c r="B26" t="s">
         <v>2986</v>
-      </c>
-      <c r="B26" t="s">
-        <v>2987</v>
       </c>
       <c r="C26" t="s">
         <v>2941</v>
@@ -75865,10 +75925,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
+        <v>2987</v>
+      </c>
+      <c r="B27" t="s">
         <v>2988</v>
-      </c>
-      <c r="B27" t="s">
-        <v>2989</v>
       </c>
       <c r="C27" t="s">
         <v>2941</v>
@@ -75876,10 +75936,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
+        <v>2989</v>
+      </c>
+      <c r="B28" t="s">
         <v>2990</v>
-      </c>
-      <c r="B28" t="s">
-        <v>2985</v>
       </c>
       <c r="C28" t="s">
         <v>2941</v>
@@ -75901,7 +75961,7 @@
         <v>2993</v>
       </c>
       <c r="B30" t="s">
-        <v>2994</v>
+        <v>2988</v>
       </c>
       <c r="C30" t="s">
         <v>2941</v>
@@ -75909,10 +75969,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
+        <v>2994</v>
+      </c>
+      <c r="B31" t="s">
         <v>2995</v>
-      </c>
-      <c r="B31" t="s">
-        <v>2996</v>
       </c>
       <c r="C31" t="s">
         <v>2941</v>
@@ -75920,10 +75980,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
+        <v>2996</v>
+      </c>
+      <c r="B32" t="s">
         <v>2997</v>
-      </c>
-      <c r="B32" t="s">
-        <v>2998</v>
       </c>
       <c r="C32" t="s">
         <v>2941</v>
@@ -75931,21 +75991,21 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
+        <v>2998</v>
+      </c>
+      <c r="B33" t="s">
         <v>2999</v>
       </c>
-      <c r="B33" t="s">
-        <v>3000</v>
-      </c>
       <c r="C33" t="s">
-        <v>2938</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
+        <v>3000</v>
+      </c>
+      <c r="B34" t="s">
         <v>3001</v>
-      </c>
-      <c r="B34" t="s">
-        <v>3002</v>
       </c>
       <c r="C34" t="s">
         <v>2941</v>
@@ -75953,10 +76013,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
+        <v>3002</v>
+      </c>
+      <c r="B35" t="s">
         <v>3003</v>
-      </c>
-      <c r="B35" t="s">
-        <v>3004</v>
       </c>
       <c r="C35" t="s">
         <v>2941</v>
@@ -75964,10 +76024,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
+        <v>3004</v>
+      </c>
+      <c r="B36" t="s">
         <v>3005</v>
-      </c>
-      <c r="B36" t="s">
-        <v>3006</v>
       </c>
       <c r="C36" t="s">
         <v>2941</v>
@@ -75975,32 +76035,32 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
+        <v>3006</v>
+      </c>
+      <c r="B37" t="s">
         <v>3007</v>
       </c>
-      <c r="B37" t="s">
-        <v>3008</v>
-      </c>
       <c r="C37" t="s">
-        <v>2941</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
+        <v>3008</v>
+      </c>
+      <c r="B38" t="s">
         <v>3009</v>
       </c>
-      <c r="B38" t="s">
-        <v>3010</v>
-      </c>
       <c r="C38" t="s">
-        <v>2938</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>3010</v>
+      </c>
+      <c r="B39" t="s">
         <v>3011</v>
-      </c>
-      <c r="B39" t="s">
-        <v>3012</v>
       </c>
       <c r="C39" t="s">
         <v>2941</v>
@@ -76008,10 +76068,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>3012</v>
+      </c>
+      <c r="B40" t="s">
         <v>3013</v>
-      </c>
-      <c r="B40" t="s">
-        <v>3014</v>
       </c>
       <c r="C40" t="s">
         <v>2941</v>
@@ -76019,10 +76079,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>3014</v>
+      </c>
+      <c r="B41" t="s">
         <v>3015</v>
-      </c>
-      <c r="B41" t="s">
-        <v>3016</v>
       </c>
       <c r="C41" t="s">
         <v>2941</v>
@@ -76030,10 +76090,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
+        <v>3016</v>
+      </c>
+      <c r="B42" t="s">
         <v>3017</v>
-      </c>
-      <c r="B42" t="s">
-        <v>3018</v>
       </c>
       <c r="C42" t="s">
         <v>2941</v>
@@ -76041,10 +76101,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="B43" t="s">
-        <v>3020</v>
+        <v>2978</v>
       </c>
       <c r="C43" t="s">
         <v>2941</v>
@@ -76052,21 +76112,21 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>3021</v>
+        <v>3019</v>
       </c>
       <c r="B44" t="s">
-        <v>3022</v>
+        <v>3020</v>
       </c>
       <c r="C44" t="s">
-        <v>2941</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>3023</v>
+        <v>3021</v>
       </c>
       <c r="B45" t="s">
-        <v>3024</v>
+        <v>3022</v>
       </c>
       <c r="C45" t="s">
         <v>2941</v>
@@ -76074,10 +76134,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>3025</v>
+        <v>3023</v>
       </c>
       <c r="B46" t="s">
-        <v>3026</v>
+        <v>3024</v>
       </c>
       <c r="C46" t="s">
         <v>2941</v>
@@ -76085,21 +76145,21 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>3025</v>
       </c>
       <c r="B47" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="C47" t="s">
-        <v>2938</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
+        <v>3027</v>
+      </c>
+      <c r="B48" t="s">
         <v>3028</v>
-      </c>
-      <c r="B48" t="s">
-        <v>3029</v>
       </c>
       <c r="C48" t="s">
         <v>2941</v>
@@ -76107,10 +76167,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
+        <v>3029</v>
+      </c>
+      <c r="B49" t="s">
         <v>3030</v>
-      </c>
-      <c r="B49" t="s">
-        <v>3031</v>
       </c>
       <c r="C49" t="s">
         <v>2941</v>
@@ -76118,10 +76178,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
+        <v>3031</v>
+      </c>
+      <c r="B50" t="s">
         <v>3032</v>
-      </c>
-      <c r="B50" t="s">
-        <v>3033</v>
       </c>
       <c r="C50" t="s">
         <v>2941</v>
@@ -76129,10 +76189,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
+        <v>3033</v>
+      </c>
+      <c r="B51" t="s">
         <v>3034</v>
-      </c>
-      <c r="B51" t="s">
-        <v>3035</v>
       </c>
       <c r="C51" t="s">
         <v>2941</v>
@@ -76140,10 +76200,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
+        <v>3035</v>
+      </c>
+      <c r="B52" t="s">
         <v>3036</v>
-      </c>
-      <c r="B52" t="s">
-        <v>3037</v>
       </c>
       <c r="C52" t="s">
         <v>2941</v>
@@ -76151,10 +76211,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
+        <v>3037</v>
+      </c>
+      <c r="B53" t="s">
         <v>3038</v>
-      </c>
-      <c r="B53" t="s">
-        <v>3039</v>
       </c>
       <c r="C53" t="s">
         <v>2941</v>
@@ -76162,32 +76222,32 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>3040</v>
+        <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>3041</v>
+        <v>3039</v>
       </c>
       <c r="C54" t="s">
-        <v>2941</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>3042</v>
+        <v>3040</v>
       </c>
       <c r="B55" t="s">
-        <v>3043</v>
+        <v>3041</v>
       </c>
       <c r="C55" t="s">
-        <v>3044</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>3045</v>
+        <v>3042</v>
       </c>
       <c r="B56" t="s">
-        <v>3046</v>
+        <v>3043</v>
       </c>
       <c r="C56" t="s">
         <v>2941</v>
@@ -76195,21 +76255,21 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>3047</v>
+        <v>3044</v>
       </c>
       <c r="B57" t="s">
-        <v>3048</v>
+        <v>3045</v>
       </c>
       <c r="C57" t="s">
-        <v>2938</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>3049</v>
+        <v>3046</v>
       </c>
       <c r="B58" t="s">
-        <v>3050</v>
+        <v>3047</v>
       </c>
       <c r="C58" t="s">
         <v>2941</v>
@@ -76217,10 +76277,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>3051</v>
+        <v>3048</v>
       </c>
       <c r="B59" t="s">
-        <v>3052</v>
+        <v>3049</v>
       </c>
       <c r="C59" t="s">
         <v>2941</v>
@@ -76228,10 +76288,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>3053</v>
+        <v>3050</v>
       </c>
       <c r="B60" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="C60" t="s">
         <v>2941</v>
@@ -76239,10 +76299,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>3055</v>
+        <v>3052</v>
       </c>
       <c r="B61" t="s">
-        <v>3056</v>
+        <v>3053</v>
       </c>
       <c r="C61" t="s">
         <v>2941</v>
@@ -76250,21 +76310,21 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="B62" t="s">
-        <v>3058</v>
+        <v>3055</v>
       </c>
       <c r="C62" t="s">
-        <v>2941</v>
+        <v>3056</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>3059</v>
+        <v>3057</v>
       </c>
       <c r="B63" t="s">
-        <v>3060</v>
+        <v>3058</v>
       </c>
       <c r="C63" t="s">
         <v>2941</v>
@@ -76272,10 +76332,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
       <c r="B64" t="s">
-        <v>3062</v>
+        <v>3060</v>
       </c>
       <c r="C64" t="s">
         <v>2941</v>
@@ -76283,21 +76343,21 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>3063</v>
+        <v>3061</v>
       </c>
       <c r="B65" t="s">
-        <v>3064</v>
+        <v>3062</v>
       </c>
       <c r="C65" t="s">
-        <v>2941</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>3065</v>
+        <v>3063</v>
       </c>
       <c r="B66" t="s">
-        <v>3066</v>
+        <v>3064</v>
       </c>
       <c r="C66" t="s">
         <v>2941</v>
@@ -76305,10 +76365,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>3067</v>
+        <v>3065</v>
       </c>
       <c r="B67" t="s">
-        <v>2973</v>
+        <v>3066</v>
       </c>
       <c r="C67" t="s">
         <v>2941</v>
@@ -76316,10 +76376,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
+        <v>3067</v>
+      </c>
+      <c r="B68" t="s">
         <v>3068</v>
-      </c>
-      <c r="B68" t="s">
-        <v>3069</v>
       </c>
       <c r="C68" t="s">
         <v>2941</v>
@@ -76327,10 +76387,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
+        <v>3069</v>
+      </c>
+      <c r="B69" t="s">
         <v>3070</v>
-      </c>
-      <c r="B69" t="s">
-        <v>3071</v>
       </c>
       <c r="C69" t="s">
         <v>2941</v>
@@ -76338,10 +76398,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
+        <v>3071</v>
+      </c>
+      <c r="B70" t="s">
         <v>3072</v>
-      </c>
-      <c r="B70" t="s">
-        <v>3073</v>
       </c>
       <c r="C70" t="s">
         <v>2941</v>
@@ -76349,12 +76409,133 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
+        <v>3073</v>
+      </c>
+      <c r="B71" t="s">
         <v>3074</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
         <v>3075</v>
       </c>
-      <c r="C71" t="s">
+      <c r="B72" t="s">
+        <v>3076</v>
+      </c>
+      <c r="C72" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>3077</v>
+      </c>
+      <c r="B73" t="s">
+        <v>3078</v>
+      </c>
+      <c r="C73" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>3079</v>
+      </c>
+      <c r="B74" t="s">
+        <v>3080</v>
+      </c>
+      <c r="C74" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>3081</v>
+      </c>
+      <c r="B75" t="s">
+        <v>2973</v>
+      </c>
+      <c r="C75" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>3082</v>
+      </c>
+      <c r="B76" t="s">
+        <v>3083</v>
+      </c>
+      <c r="C76" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>3084</v>
+      </c>
+      <c r="B77" t="s">
+        <v>3085</v>
+      </c>
+      <c r="C77" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>3086</v>
+      </c>
+      <c r="B78" t="s">
+        <v>3087</v>
+      </c>
+      <c r="C78" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>3088</v>
+      </c>
+      <c r="B79" t="s">
+        <v>3089</v>
+      </c>
+      <c r="C79" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>3090</v>
+      </c>
+      <c r="B80" t="s">
+        <v>3091</v>
+      </c>
+      <c r="C80" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>3092</v>
+      </c>
+      <c r="B81" t="s">
+        <v>3093</v>
+      </c>
+      <c r="C81" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>3094</v>
+      </c>
+      <c r="B82" t="s">
+        <v>3095</v>
+      </c>
+      <c r="C82" t="s">
         <v>2941</v>
       </c>
     </row>
